--- a/Result/profitability/1603.xlsx
+++ b/Result/profitability/1603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6975</v>
+        <v>0.7037500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>13.19125</v>
+        <v>13.33</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5925</v>
+        <v>0.64625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.245</v>
+        <v>13.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.52625</v>
+        <v>0.5525000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>12.755</v>
+        <v>12.8775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4275</v>
+        <v>0.44125</v>
       </c>
       <c r="N5" t="n">
-        <v>12.51125</v>
+        <v>12.83375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.325</v>
+        <v>0.30875</v>
       </c>
       <c r="N6" t="n">
-        <v>12.7075</v>
+        <v>12.99125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2175</v>
+        <v>0.3225</v>
       </c>
       <c r="N7" t="n">
-        <v>13.51</v>
+        <v>14.43125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2825</v>
+        <v>0.38</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13</v>
+        <v>16.09</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1504</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1256</v>
+      </c>
+      <c r="E75" t="n">
+        <v>248</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>215</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.32%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>214</v>
+      </c>
+      <c r="K75" t="n">
+        <v>170</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7837499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.30625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.689655172413794</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.680000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.8697621744054362</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1145833333333335</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.580000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1852117731514717</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
